--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_27-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_27-10-2025.xlsx
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff633a1e8e5+80021]
-	GetHandleVerifier [0x0x7ff633a1e940+80112]
-	(No symbol) [0x0x7ff6337a060f]
-	(No symbol) [0x0x7ff6337f8854]
-	(No symbol) [0x0x7ff6337f8b1c]
-	(No symbol) [0x0x7ff63384c927]
-	(No symbol) [0x0x7ff63382126f]
-	(No symbol) [0x0x7ff63384968a]
-	(No symbol) [0x0x7ff633821003]
-	(No symbol) [0x0x7ff6337e95d1]
-	(No symbol) [0x0x7ff6337ea3f3]
-	GetHandleVerifier [0x0x7ff633cddc7d+2960429]
-	GetHandleVerifier [0x0x7ff633cd7f3a+2936554]
-	GetHandleVerifier [0x0x7ff633cf8977+3070247]
-	GetHandleVerifier [0x0x7ff633a383ce+185214]
-	GetHandleVerifier [0x0x7ff633a3fe1f+216527]
-	GetHandleVerifier [0x0x7ff633a27b24+117460]
-	GetHandleVerifier [0x0x7ff633a27cdf+117903]
-	GetHandleVerifier [0x0x7ff633a0dbb8+11112]
+	GetHandleVerifier [0x0x7ff7c39ae8e5+80021]
+	GetHandleVerifier [0x0x7ff7c39ae940+80112]
+	(No symbol) [0x0x7ff7c373060f]
+	(No symbol) [0x0x7ff7c3788854]
+	(No symbol) [0x0x7ff7c3788b1c]
+	(No symbol) [0x0x7ff7c37dc927]
+	(No symbol) [0x0x7ff7c37b126f]
+	(No symbol) [0x0x7ff7c37d968a]
+	(No symbol) [0x0x7ff7c37b1003]
+	(No symbol) [0x0x7ff7c37795d1]
+	(No symbol) [0x0x7ff7c377a3f3]
+	GetHandleVerifier [0x0x7ff7c3c6dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c3c67f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c3c88977+3070247]
+	GetHandleVerifier [0x0x7ff7c39c83ce+185214]
+	GetHandleVerifier [0x0x7ff7c39cfe1f+216527]
+	GetHandleVerifier [0x0x7ff7c39b7b24+117460]
+	GetHandleVerifier [0x0x7ff7c39b7cdf+117903]
+	GetHandleVerifier [0x0x7ff7c399dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff633a1e8e5+80021]
-	GetHandleVerifier [0x0x7ff633a1e940+80112]
-	(No symbol) [0x0x7ff6337a060f]
-	(No symbol) [0x0x7ff6337f8854]
-	(No symbol) [0x0x7ff6337f8b1c]
-	(No symbol) [0x0x7ff63384c927]
-	(No symbol) [0x0x7ff63382126f]
-	(No symbol) [0x0x7ff63384968a]
-	(No symbol) [0x0x7ff633821003]
-	(No symbol) [0x0x7ff6337e95d1]
-	(No symbol) [0x0x7ff6337ea3f3]
-	GetHandleVerifier [0x0x7ff633cddc7d+2960429]
-	GetHandleVerifier [0x0x7ff633cd7f3a+2936554]
-	GetHandleVerifier [0x0x7ff633cf8977+3070247]
-	GetHandleVerifier [0x0x7ff633a383ce+185214]
-	GetHandleVerifier [0x0x7ff633a3fe1f+216527]
-	GetHandleVerifier [0x0x7ff633a27b24+117460]
-	GetHandleVerifier [0x0x7ff633a27cdf+117903]
-	GetHandleVerifier [0x0x7ff633a0dbb8+11112]
+	GetHandleVerifier [0x0x7ff7c39ae8e5+80021]
+	GetHandleVerifier [0x0x7ff7c39ae940+80112]
+	(No symbol) [0x0x7ff7c373060f]
+	(No symbol) [0x0x7ff7c3788854]
+	(No symbol) [0x0x7ff7c3788b1c]
+	(No symbol) [0x0x7ff7c37dc927]
+	(No symbol) [0x0x7ff7c37b126f]
+	(No symbol) [0x0x7ff7c37d968a]
+	(No symbol) [0x0x7ff7c37b1003]
+	(No symbol) [0x0x7ff7c37795d1]
+	(No symbol) [0x0x7ff7c377a3f3]
+	GetHandleVerifier [0x0x7ff7c3c6dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c3c67f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c3c88977+3070247]
+	GetHandleVerifier [0x0x7ff7c39c83ce+185214]
+	GetHandleVerifier [0x0x7ff7c39cfe1f+216527]
+	GetHandleVerifier [0x0x7ff7c39b7b24+117460]
+	GetHandleVerifier [0x0x7ff7c39b7cdf+117903]
+	GetHandleVerifier [0x0x7ff7c399dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff633a1e8e5+80021]
-	GetHandleVerifier [0x0x7ff633a1e940+80112]
-	(No symbol) [0x0x7ff6337a060f]
-	(No symbol) [0x0x7ff6337f8854]
-	(No symbol) [0x0x7ff6337f8b1c]
-	(No symbol) [0x0x7ff63384c927]
-	(No symbol) [0x0x7ff63382126f]
-	(No symbol) [0x0x7ff63384968a]
-	(No symbol) [0x0x7ff633821003]
-	(No symbol) [0x0x7ff6337e95d1]
-	(No symbol) [0x0x7ff6337ea3f3]
-	GetHandleVerifier [0x0x7ff633cddc7d+2960429]
-	GetHandleVerifier [0x0x7ff633cd7f3a+2936554]
-	GetHandleVerifier [0x0x7ff633cf8977+3070247]
-	GetHandleVerifier [0x0x7ff633a383ce+185214]
-	GetHandleVerifier [0x0x7ff633a3fe1f+216527]
-	GetHandleVerifier [0x0x7ff633a27b24+117460]
-	GetHandleVerifier [0x0x7ff633a27cdf+117903]
-	GetHandleVerifier [0x0x7ff633a0dbb8+11112]
+	GetHandleVerifier [0x0x7ff7c39ae8e5+80021]
+	GetHandleVerifier [0x0x7ff7c39ae940+80112]
+	(No symbol) [0x0x7ff7c373060f]
+	(No symbol) [0x0x7ff7c3788854]
+	(No symbol) [0x0x7ff7c3788b1c]
+	(No symbol) [0x0x7ff7c37dc927]
+	(No symbol) [0x0x7ff7c37b126f]
+	(No symbol) [0x0x7ff7c37d968a]
+	(No symbol) [0x0x7ff7c37b1003]
+	(No symbol) [0x0x7ff7c37795d1]
+	(No symbol) [0x0x7ff7c377a3f3]
+	GetHandleVerifier [0x0x7ff7c3c6dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c3c67f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c3c88977+3070247]
+	GetHandleVerifier [0x0x7ff7c39c83ce+185214]
+	GetHandleVerifier [0x0x7ff7c39cfe1f+216527]
+	GetHandleVerifier [0x0x7ff7c39b7b24+117460]
+	GetHandleVerifier [0x0x7ff7c39b7cdf+117903]
+	GetHandleVerifier [0x0x7ff7c399dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff633a1e8e5+80021]
-	GetHandleVerifier [0x0x7ff633a1e940+80112]
-	(No symbol) [0x0x7ff6337a060f]
-	(No symbol) [0x0x7ff6337f8854]
-	(No symbol) [0x0x7ff6337f8b1c]
-	(No symbol) [0x0x7ff63384c927]
-	(No symbol) [0x0x7ff63382126f]
-	(No symbol) [0x0x7ff63384968a]
-	(No symbol) [0x0x7ff633821003]
-	(No symbol) [0x0x7ff6337e95d1]
-	(No symbol) [0x0x7ff6337ea3f3]
-	GetHandleVerifier [0x0x7ff633cddc7d+2960429]
-	GetHandleVerifier [0x0x7ff633cd7f3a+2936554]
-	GetHandleVerifier [0x0x7ff633cf8977+3070247]
-	GetHandleVerifier [0x0x7ff633a383ce+185214]
-	GetHandleVerifier [0x0x7ff633a3fe1f+216527]
-	GetHandleVerifier [0x0x7ff633a27b24+117460]
-	GetHandleVerifier [0x0x7ff633a27cdf+117903]
-	GetHandleVerifier [0x0x7ff633a0dbb8+11112]
+	GetHandleVerifier [0x0x7ff7c39ae8e5+80021]
+	GetHandleVerifier [0x0x7ff7c39ae940+80112]
+	(No symbol) [0x0x7ff7c373060f]
+	(No symbol) [0x0x7ff7c3788854]
+	(No symbol) [0x0x7ff7c3788b1c]
+	(No symbol) [0x0x7ff7c37dc927]
+	(No symbol) [0x0x7ff7c37b126f]
+	(No symbol) [0x0x7ff7c37d968a]
+	(No symbol) [0x0x7ff7c37b1003]
+	(No symbol) [0x0x7ff7c37795d1]
+	(No symbol) [0x0x7ff7c377a3f3]
+	GetHandleVerifier [0x0x7ff7c3c6dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c3c67f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c3c88977+3070247]
+	GetHandleVerifier [0x0x7ff7c39c83ce+185214]
+	GetHandleVerifier [0x0x7ff7c39cfe1f+216527]
+	GetHandleVerifier [0x0x7ff7c39b7b24+117460]
+	GetHandleVerifier [0x0x7ff7c39b7cdf+117903]
+	GetHandleVerifier [0x0x7ff7c399dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff633a1e8e5+80021]
-	GetHandleVerifier [0x0x7ff633a1e940+80112]
-	(No symbol) [0x0x7ff6337a060f]
-	(No symbol) [0x0x7ff6337f8854]
-	(No symbol) [0x0x7ff6337f8b1c]
-	(No symbol) [0x0x7ff63384c927]
-	(No symbol) [0x0x7ff63382126f]
-	(No symbol) [0x0x7ff63384968a]
-	(No symbol) [0x0x7ff633821003]
-	(No symbol) [0x0x7ff6337e95d1]
-	(No symbol) [0x0x7ff6337ea3f3]
-	GetHandleVerifier [0x0x7ff633cddc7d+2960429]
-	GetHandleVerifier [0x0x7ff633cd7f3a+2936554]
-	GetHandleVerifier [0x0x7ff633cf8977+3070247]
-	GetHandleVerifier [0x0x7ff633a383ce+185214]
-	GetHandleVerifier [0x0x7ff633a3fe1f+216527]
-	GetHandleVerifier [0x0x7ff633a27b24+117460]
-	GetHandleVerifier [0x0x7ff633a27cdf+117903]
-	GetHandleVerifier [0x0x7ff633a0dbb8+11112]
+	GetHandleVerifier [0x0x7ff7c39ae8e5+80021]
+	GetHandleVerifier [0x0x7ff7c39ae940+80112]
+	(No symbol) [0x0x7ff7c373060f]
+	(No symbol) [0x0x7ff7c3788854]
+	(No symbol) [0x0x7ff7c3788b1c]
+	(No symbol) [0x0x7ff7c37dc927]
+	(No symbol) [0x0x7ff7c37b126f]
+	(No symbol) [0x0x7ff7c37d968a]
+	(No symbol) [0x0x7ff7c37b1003]
+	(No symbol) [0x0x7ff7c37795d1]
+	(No symbol) [0x0x7ff7c377a3f3]
+	GetHandleVerifier [0x0x7ff7c3c6dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c3c67f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c3c88977+3070247]
+	GetHandleVerifier [0x0x7ff7c39c83ce+185214]
+	GetHandleVerifier [0x0x7ff7c39cfe1f+216527]
+	GetHandleVerifier [0x0x7ff7c39b7b24+117460]
+	GetHandleVerifier [0x0x7ff7c39b7cdf+117903]
+	GetHandleVerifier [0x0x7ff7c399dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff633a1e8e5+80021]
-	GetHandleVerifier [0x0x7ff633a1e940+80112]
-	(No symbol) [0x0x7ff6337a060f]
-	(No symbol) [0x0x7ff6337f8854]
-	(No symbol) [0x0x7ff6337f8b1c]
-	(No symbol) [0x0x7ff63384c927]
-	(No symbol) [0x0x7ff63382126f]
-	(No symbol) [0x0x7ff63384968a]
-	(No symbol) [0x0x7ff633821003]
-	(No symbol) [0x0x7ff6337e95d1]
-	(No symbol) [0x0x7ff6337ea3f3]
-	GetHandleVerifier [0x0x7ff633cddc7d+2960429]
-	GetHandleVerifier [0x0x7ff633cd7f3a+2936554]
-	GetHandleVerifier [0x0x7ff633cf8977+3070247]
-	GetHandleVerifier [0x0x7ff633a383ce+185214]
-	GetHandleVerifier [0x0x7ff633a3fe1f+216527]
-	GetHandleVerifier [0x0x7ff633a27b24+117460]
-	GetHandleVerifier [0x0x7ff633a27cdf+117903]
-	GetHandleVerifier [0x0x7ff633a0dbb8+11112]
+	GetHandleVerifier [0x0x7ff7c39ae8e5+80021]
+	GetHandleVerifier [0x0x7ff7c39ae940+80112]
+	(No symbol) [0x0x7ff7c373060f]
+	(No symbol) [0x0x7ff7c3788854]
+	(No symbol) [0x0x7ff7c3788b1c]
+	(No symbol) [0x0x7ff7c37dc927]
+	(No symbol) [0x0x7ff7c37b126f]
+	(No symbol) [0x0x7ff7c37d968a]
+	(No symbol) [0x0x7ff7c37b1003]
+	(No symbol) [0x0x7ff7c37795d1]
+	(No symbol) [0x0x7ff7c377a3f3]
+	GetHandleVerifier [0x0x7ff7c3c6dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c3c67f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c3c88977+3070247]
+	GetHandleVerifier [0x0x7ff7c39c83ce+185214]
+	GetHandleVerifier [0x0x7ff7c39cfe1f+216527]
+	GetHandleVerifier [0x0x7ff7c39b7b24+117460]
+	GetHandleVerifier [0x0x7ff7c39b7cdf+117903]
+	GetHandleVerifier [0x0x7ff7c399dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff633a1e8e5+80021]
-	GetHandleVerifier [0x0x7ff633a1e940+80112]
-	(No symbol) [0x0x7ff6337a060f]
-	(No symbol) [0x0x7ff6337f8854]
-	(No symbol) [0x0x7ff6337f8b1c]
-	(No symbol) [0x0x7ff63384c927]
-	(No symbol) [0x0x7ff63382126f]
-	(No symbol) [0x0x7ff63384968a]
-	(No symbol) [0x0x7ff633821003]
-	(No symbol) [0x0x7ff6337e95d1]
-	(No symbol) [0x0x7ff6337ea3f3]
-	GetHandleVerifier [0x0x7ff633cddc7d+2960429]
-	GetHandleVerifier [0x0x7ff633cd7f3a+2936554]
-	GetHandleVerifier [0x0x7ff633cf8977+3070247]
-	GetHandleVerifier [0x0x7ff633a383ce+185214]
-	GetHandleVerifier [0x0x7ff633a3fe1f+216527]
-	GetHandleVerifier [0x0x7ff633a27b24+117460]
-	GetHandleVerifier [0x0x7ff633a27cdf+117903]
-	GetHandleVerifier [0x0x7ff633a0dbb8+11112]
+	GetHandleVerifier [0x0x7ff7c39ae8e5+80021]
+	GetHandleVerifier [0x0x7ff7c39ae940+80112]
+	(No symbol) [0x0x7ff7c373060f]
+	(No symbol) [0x0x7ff7c3788854]
+	(No symbol) [0x0x7ff7c3788b1c]
+	(No symbol) [0x0x7ff7c37dc927]
+	(No symbol) [0x0x7ff7c37b126f]
+	(No symbol) [0x0x7ff7c37d968a]
+	(No symbol) [0x0x7ff7c37b1003]
+	(No symbol) [0x0x7ff7c37795d1]
+	(No symbol) [0x0x7ff7c377a3f3]
+	GetHandleVerifier [0x0x7ff7c3c6dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c3c67f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c3c88977+3070247]
+	GetHandleVerifier [0x0x7ff7c39c83ce+185214]
+	GetHandleVerifier [0x0x7ff7c39cfe1f+216527]
+	GetHandleVerifier [0x0x7ff7c39b7b24+117460]
+	GetHandleVerifier [0x0x7ff7c39b7cdf+117903]
+	GetHandleVerifier [0x0x7ff7c399dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff633a1e8e5+80021]
-	GetHandleVerifier [0x0x7ff633a1e940+80112]
-	(No symbol) [0x0x7ff6337a060f]
-	(No symbol) [0x0x7ff6337f8854]
-	(No symbol) [0x0x7ff6337f8b1c]
-	(No symbol) [0x0x7ff63384c927]
-	(No symbol) [0x0x7ff63382126f]
-	(No symbol) [0x0x7ff63384968a]
-	(No symbol) [0x0x7ff633821003]
-	(No symbol) [0x0x7ff6337e95d1]
-	(No symbol) [0x0x7ff6337ea3f3]
-	GetHandleVerifier [0x0x7ff633cddc7d+2960429]
-	GetHandleVerifier [0x0x7ff633cd7f3a+2936554]
-	GetHandleVerifier [0x0x7ff633cf8977+3070247]
-	GetHandleVerifier [0x0x7ff633a383ce+185214]
-	GetHandleVerifier [0x0x7ff633a3fe1f+216527]
-	GetHandleVerifier [0x0x7ff633a27b24+117460]
-	GetHandleVerifier [0x0x7ff633a27cdf+117903]
-	GetHandleVerifier [0x0x7ff633a0dbb8+11112]
+	GetHandleVerifier [0x0x7ff7c39ae8e5+80021]
+	GetHandleVerifier [0x0x7ff7c39ae940+80112]
+	(No symbol) [0x0x7ff7c373060f]
+	(No symbol) [0x0x7ff7c3788854]
+	(No symbol) [0x0x7ff7c3788b1c]
+	(No symbol) [0x0x7ff7c37dc927]
+	(No symbol) [0x0x7ff7c37b126f]
+	(No symbol) [0x0x7ff7c37d968a]
+	(No symbol) [0x0x7ff7c37b1003]
+	(No symbol) [0x0x7ff7c37795d1]
+	(No symbol) [0x0x7ff7c377a3f3]
+	GetHandleVerifier [0x0x7ff7c3c6dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c3c67f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c3c88977+3070247]
+	GetHandleVerifier [0x0x7ff7c39c83ce+185214]
+	GetHandleVerifier [0x0x7ff7c39cfe1f+216527]
+	GetHandleVerifier [0x0x7ff7c39b7b24+117460]
+	GetHandleVerifier [0x0x7ff7c39b7cdf+117903]
+	GetHandleVerifier [0x0x7ff7c399dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff633a1e8e5+80021]
-	GetHandleVerifier [0x0x7ff633a1e940+80112]
-	(No symbol) [0x0x7ff6337a060f]
-	(No symbol) [0x0x7ff6337f8854]
-	(No symbol) [0x0x7ff6337f8b1c]
-	(No symbol) [0x0x7ff63384c927]
-	(No symbol) [0x0x7ff63382126f]
-	(No symbol) [0x0x7ff63384968a]
-	(No symbol) [0x0x7ff633821003]
-	(No symbol) [0x0x7ff6337e95d1]
-	(No symbol) [0x0x7ff6337ea3f3]
-	GetHandleVerifier [0x0x7ff633cddc7d+2960429]
-	GetHandleVerifier [0x0x7ff633cd7f3a+2936554]
-	GetHandleVerifier [0x0x7ff633cf8977+3070247]
-	GetHandleVerifier [0x0x7ff633a383ce+185214]
-	GetHandleVerifier [0x0x7ff633a3fe1f+216527]
-	GetHandleVerifier [0x0x7ff633a27b24+117460]
-	GetHandleVerifier [0x0x7ff633a27cdf+117903]
-	GetHandleVerifier [0x0x7ff633a0dbb8+11112]
+	GetHandleVerifier [0x0x7ff7c39ae8e5+80021]
+	GetHandleVerifier [0x0x7ff7c39ae940+80112]
+	(No symbol) [0x0x7ff7c373060f]
+	(No symbol) [0x0x7ff7c3788854]
+	(No symbol) [0x0x7ff7c3788b1c]
+	(No symbol) [0x0x7ff7c37dc927]
+	(No symbol) [0x0x7ff7c37b126f]
+	(No symbol) [0x0x7ff7c37d968a]
+	(No symbol) [0x0x7ff7c37b1003]
+	(No symbol) [0x0x7ff7c37795d1]
+	(No symbol) [0x0x7ff7c377a3f3]
+	GetHandleVerifier [0x0x7ff7c3c6dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c3c67f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c3c88977+3070247]
+	GetHandleVerifier [0x0x7ff7c39c83ce+185214]
+	GetHandleVerifier [0x0x7ff7c39cfe1f+216527]
+	GetHandleVerifier [0x0x7ff7c39b7b24+117460]
+	GetHandleVerifier [0x0x7ff7c39b7cdf+117903]
+	GetHandleVerifier [0x0x7ff7c399dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff633a1e8e5+80021]
-	GetHandleVerifier [0x0x7ff633a1e940+80112]
-	(No symbol) [0x0x7ff6337a060f]
-	(No symbol) [0x0x7ff6337f8854]
-	(No symbol) [0x0x7ff6337f8b1c]
-	(No symbol) [0x0x7ff63384c927]
-	(No symbol) [0x0x7ff63382126f]
-	(No symbol) [0x0x7ff63384968a]
-	(No symbol) [0x0x7ff633821003]
-	(No symbol) [0x0x7ff6337e95d1]
-	(No symbol) [0x0x7ff6337ea3f3]
-	GetHandleVerifier [0x0x7ff633cddc7d+2960429]
-	GetHandleVerifier [0x0x7ff633cd7f3a+2936554]
-	GetHandleVerifier [0x0x7ff633cf8977+3070247]
-	GetHandleVerifier [0x0x7ff633a383ce+185214]
-	GetHandleVerifier [0x0x7ff633a3fe1f+216527]
-	GetHandleVerifier [0x0x7ff633a27b24+117460]
-	GetHandleVerifier [0x0x7ff633a27cdf+117903]
-	GetHandleVerifier [0x0x7ff633a0dbb8+11112]
+	GetHandleVerifier [0x0x7ff7c39ae8e5+80021]
+	GetHandleVerifier [0x0x7ff7c39ae940+80112]
+	(No symbol) [0x0x7ff7c373060f]
+	(No symbol) [0x0x7ff7c3788854]
+	(No symbol) [0x0x7ff7c3788b1c]
+	(No symbol) [0x0x7ff7c37dc927]
+	(No symbol) [0x0x7ff7c37b126f]
+	(No symbol) [0x0x7ff7c37d968a]
+	(No symbol) [0x0x7ff7c37b1003]
+	(No symbol) [0x0x7ff7c37795d1]
+	(No symbol) [0x0x7ff7c377a3f3]
+	GetHandleVerifier [0x0x7ff7c3c6dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c3c67f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c3c88977+3070247]
+	GetHandleVerifier [0x0x7ff7c39c83ce+185214]
+	GetHandleVerifier [0x0x7ff7c39cfe1f+216527]
+	GetHandleVerifier [0x0x7ff7c39b7b24+117460]
+	GetHandleVerifier [0x0x7ff7c39b7cdf+117903]
+	GetHandleVerifier [0x0x7ff7c399dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff633a1e8e5+80021]
-	GetHandleVerifier [0x0x7ff633a1e940+80112]
-	(No symbol) [0x0x7ff6337a060f]
-	(No symbol) [0x0x7ff6337f8854]
-	(No symbol) [0x0x7ff6337f8b1c]
-	(No symbol) [0x0x7ff63384c927]
-	(No symbol) [0x0x7ff63382126f]
-	(No symbol) [0x0x7ff63384968a]
-	(No symbol) [0x0x7ff633821003]
-	(No symbol) [0x0x7ff6337e95d1]
-	(No symbol) [0x0x7ff6337ea3f3]
-	GetHandleVerifier [0x0x7ff633cddc7d+2960429]
-	GetHandleVerifier [0x0x7ff633cd7f3a+2936554]
-	GetHandleVerifier [0x0x7ff633cf8977+3070247]
-	GetHandleVerifier [0x0x7ff633a383ce+185214]
-	GetHandleVerifier [0x0x7ff633a3fe1f+216527]
-	GetHandleVerifier [0x0x7ff633a27b24+117460]
-	GetHandleVerifier [0x0x7ff633a27cdf+117903]
-	GetHandleVerifier [0x0x7ff633a0dbb8+11112]
+	GetHandleVerifier [0x0x7ff7c39ae8e5+80021]
+	GetHandleVerifier [0x0x7ff7c39ae940+80112]
+	(No symbol) [0x0x7ff7c373060f]
+	(No symbol) [0x0x7ff7c3788854]
+	(No symbol) [0x0x7ff7c3788b1c]
+	(No symbol) [0x0x7ff7c37dc927]
+	(No symbol) [0x0x7ff7c37b126f]
+	(No symbol) [0x0x7ff7c37d968a]
+	(No symbol) [0x0x7ff7c37b1003]
+	(No symbol) [0x0x7ff7c37795d1]
+	(No symbol) [0x0x7ff7c377a3f3]
+	GetHandleVerifier [0x0x7ff7c3c6dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c3c67f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c3c88977+3070247]
+	GetHandleVerifier [0x0x7ff7c39c83ce+185214]
+	GetHandleVerifier [0x0x7ff7c39cfe1f+216527]
+	GetHandleVerifier [0x0x7ff7c39b7b24+117460]
+	GetHandleVerifier [0x0x7ff7c39b7cdf+117903]
+	GetHandleVerifier [0x0x7ff7c399dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff633a1e8e5+80021]
-	GetHandleVerifier [0x0x7ff633a1e940+80112]
-	(No symbol) [0x0x7ff6337a060f]
-	(No symbol) [0x0x7ff6337f8854]
-	(No symbol) [0x0x7ff6337f8b1c]
-	(No symbol) [0x0x7ff63384c927]
-	(No symbol) [0x0x7ff63382126f]
-	(No symbol) [0x0x7ff63384968a]
-	(No symbol) [0x0x7ff633821003]
-	(No symbol) [0x0x7ff6337e95d1]
-	(No symbol) [0x0x7ff6337ea3f3]
-	GetHandleVerifier [0x0x7ff633cddc7d+2960429]
-	GetHandleVerifier [0x0x7ff633cd7f3a+2936554]
-	GetHandleVerifier [0x0x7ff633cf8977+3070247]
-	GetHandleVerifier [0x0x7ff633a383ce+185214]
-	GetHandleVerifier [0x0x7ff633a3fe1f+216527]
-	GetHandleVerifier [0x0x7ff633a27b24+117460]
-	GetHandleVerifier [0x0x7ff633a27cdf+117903]
-	GetHandleVerifier [0x0x7ff633a0dbb8+11112]
+	GetHandleVerifier [0x0x7ff6998fe8e5+80021]
+	GetHandleVerifier [0x0x7ff6998fe940+80112]
+	(No symbol) [0x0x7ff69968060f]
+	(No symbol) [0x0x7ff6996d8854]
+	(No symbol) [0x0x7ff6996d8b1c]
+	(No symbol) [0x0x7ff69972c927]
+	(No symbol) [0x0x7ff69970126f]
+	(No symbol) [0x0x7ff69972968a]
+	(No symbol) [0x0x7ff699701003]
+	(No symbol) [0x0x7ff6996c95d1]
+	(No symbol) [0x0x7ff6996ca3f3]
+	GetHandleVerifier [0x0x7ff699bbdc7d+2960429]
+	GetHandleVerifier [0x0x7ff699bb7f3a+2936554]
+	GetHandleVerifier [0x0x7ff699bd8977+3070247]
+	GetHandleVerifier [0x0x7ff6999183ce+185214]
+	GetHandleVerifier [0x0x7ff69991fe1f+216527]
+	GetHandleVerifier [0x0x7ff699907b24+117460]
+	GetHandleVerifier [0x0x7ff699907cdf+117903]
+	GetHandleVerifier [0x0x7ff6998edbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff633a1e8e5+80021]
-	GetHandleVerifier [0x0x7ff633a1e940+80112]
-	(No symbol) [0x0x7ff6337a060f]
-	(No symbol) [0x0x7ff6337f8854]
-	(No symbol) [0x0x7ff6337f8b1c]
-	(No symbol) [0x0x7ff63384c927]
-	(No symbol) [0x0x7ff63382126f]
-	(No symbol) [0x0x7ff63384968a]
-	(No symbol) [0x0x7ff633821003]
-	(No symbol) [0x0x7ff6337e95d1]
-	(No symbol) [0x0x7ff6337ea3f3]
-	GetHandleVerifier [0x0x7ff633cddc7d+2960429]
-	GetHandleVerifier [0x0x7ff633cd7f3a+2936554]
-	GetHandleVerifier [0x0x7ff633cf8977+3070247]
-	GetHandleVerifier [0x0x7ff633a383ce+185214]
-	GetHandleVerifier [0x0x7ff633a3fe1f+216527]
-	GetHandleVerifier [0x0x7ff633a27b24+117460]
-	GetHandleVerifier [0x0x7ff633a27cdf+117903]
-	GetHandleVerifier [0x0x7ff633a0dbb8+11112]
+	GetHandleVerifier [0x0x7ff6998fe8e5+80021]
+	GetHandleVerifier [0x0x7ff6998fe940+80112]
+	(No symbol) [0x0x7ff69968060f]
+	(No symbol) [0x0x7ff6996d8854]
+	(No symbol) [0x0x7ff6996d8b1c]
+	(No symbol) [0x0x7ff69972c927]
+	(No symbol) [0x0x7ff69970126f]
+	(No symbol) [0x0x7ff69972968a]
+	(No symbol) [0x0x7ff699701003]
+	(No symbol) [0x0x7ff6996c95d1]
+	(No symbol) [0x0x7ff6996ca3f3]
+	GetHandleVerifier [0x0x7ff699bbdc7d+2960429]
+	GetHandleVerifier [0x0x7ff699bb7f3a+2936554]
+	GetHandleVerifier [0x0x7ff699bd8977+3070247]
+	GetHandleVerifier [0x0x7ff6999183ce+185214]
+	GetHandleVerifier [0x0x7ff69991fe1f+216527]
+	GetHandleVerifier [0x0x7ff699907b24+117460]
+	GetHandleVerifier [0x0x7ff699907cdf+117903]
+	GetHandleVerifier [0x0x7ff6998edbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£38.64</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff633a1e8e5+80021]
-	GetHandleVerifier [0x0x7ff633a1e940+80112]
-	(No symbol) [0x0x7ff6337a060f]
-	(No symbol) [0x0x7ff6337f8854]
-	(No symbol) [0x0x7ff6337f8b1c]
-	(No symbol) [0x0x7ff63384c927]
-	(No symbol) [0x0x7ff63382126f]
-	(No symbol) [0x0x7ff63384968a]
-	(No symbol) [0x0x7ff633821003]
-	(No symbol) [0x0x7ff6337e95d1]
-	(No symbol) [0x0x7ff6337ea3f3]
-	GetHandleVerifier [0x0x7ff633cddc7d+2960429]
-	GetHandleVerifier [0x0x7ff633cd7f3a+2936554]
-	GetHandleVerifier [0x0x7ff633cf8977+3070247]
-	GetHandleVerifier [0x0x7ff633a383ce+185214]
-	GetHandleVerifier [0x0x7ff633a3fe1f+216527]
-	GetHandleVerifier [0x0x7ff633a27b24+117460]
-	GetHandleVerifier [0x0x7ff633a27cdf+117903]
-	GetHandleVerifier [0x0x7ff633a0dbb8+11112]
+	GetHandleVerifier [0x0x7ff6998fe8e5+80021]
+	GetHandleVerifier [0x0x7ff6998fe940+80112]
+	(No symbol) [0x0x7ff69968060f]
+	(No symbol) [0x0x7ff6996d8854]
+	(No symbol) [0x0x7ff6996d8b1c]
+	(No symbol) [0x0x7ff69972c927]
+	(No symbol) [0x0x7ff69970126f]
+	(No symbol) [0x0x7ff69972968a]
+	(No symbol) [0x0x7ff699701003]
+	(No symbol) [0x0x7ff6996c95d1]
+	(No symbol) [0x0x7ff6996ca3f3]
+	GetHandleVerifier [0x0x7ff699bbdc7d+2960429]
+	GetHandleVerifier [0x0x7ff699bb7f3a+2936554]
+	GetHandleVerifier [0x0x7ff699bd8977+3070247]
+	GetHandleVerifier [0x0x7ff6999183ce+185214]
+	GetHandleVerifier [0x0x7ff69991fe1f+216527]
+	GetHandleVerifier [0x0x7ff699907b24+117460]
+	GetHandleVerifier [0x0x7ff699907cdf+117903]
+	GetHandleVerifier [0x0x7ff6998edbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff633a1e8e5+80021]
-	GetHandleVerifier [0x0x7ff633a1e940+80112]
-	(No symbol) [0x0x7ff6337a060f]
-	(No symbol) [0x0x7ff6337f8854]
-	(No symbol) [0x0x7ff6337f8b1c]
-	(No symbol) [0x0x7ff63384c927]
-	(No symbol) [0x0x7ff63382126f]
-	(No symbol) [0x0x7ff63384968a]
-	(No symbol) [0x0x7ff633821003]
-	(No symbol) [0x0x7ff6337e95d1]
-	(No symbol) [0x0x7ff6337ea3f3]
-	GetHandleVerifier [0x0x7ff633cddc7d+2960429]
-	GetHandleVerifier [0x0x7ff633cd7f3a+2936554]
-	GetHandleVerifier [0x0x7ff633cf8977+3070247]
-	GetHandleVerifier [0x0x7ff633a383ce+185214]
-	GetHandleVerifier [0x0x7ff633a3fe1f+216527]
-	GetHandleVerifier [0x0x7ff633a27b24+117460]
-	GetHandleVerifier [0x0x7ff633a27cdf+117903]
-	GetHandleVerifier [0x0x7ff633a0dbb8+11112]
+	GetHandleVerifier [0x0x7ff6998fe8e5+80021]
+	GetHandleVerifier [0x0x7ff6998fe940+80112]
+	(No symbol) [0x0x7ff69968060f]
+	(No symbol) [0x0x7ff6996d8854]
+	(No symbol) [0x0x7ff6996d8b1c]
+	(No symbol) [0x0x7ff69972c927]
+	(No symbol) [0x0x7ff69970126f]
+	(No symbol) [0x0x7ff69972968a]
+	(No symbol) [0x0x7ff699701003]
+	(No symbol) [0x0x7ff6996c95d1]
+	(No symbol) [0x0x7ff6996ca3f3]
+	GetHandleVerifier [0x0x7ff699bbdc7d+2960429]
+	GetHandleVerifier [0x0x7ff699bb7f3a+2936554]
+	GetHandleVerifier [0x0x7ff699bd8977+3070247]
+	GetHandleVerifier [0x0x7ff6999183ce+185214]
+	GetHandleVerifier [0x0x7ff69991fe1f+216527]
+	GetHandleVerifier [0x0x7ff699907b24+117460]
+	GetHandleVerifier [0x0x7ff699907cdf+117903]
+	GetHandleVerifier [0x0x7ff6998edbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff633a1e8e5+80021]
-	GetHandleVerifier [0x0x7ff633a1e940+80112]
-	(No symbol) [0x0x7ff6337a060f]
-	(No symbol) [0x0x7ff6337f8854]
-	(No symbol) [0x0x7ff6337f8b1c]
-	(No symbol) [0x0x7ff63384c927]
-	(No symbol) [0x0x7ff63382126f]
-	(No symbol) [0x0x7ff63384968a]
-	(No symbol) [0x0x7ff633821003]
-	(No symbol) [0x0x7ff6337e95d1]
-	(No symbol) [0x0x7ff6337ea3f3]
-	GetHandleVerifier [0x0x7ff633cddc7d+2960429]
-	GetHandleVerifier [0x0x7ff633cd7f3a+2936554]
-	GetHandleVerifier [0x0x7ff633cf8977+3070247]
-	GetHandleVerifier [0x0x7ff633a383ce+185214]
-	GetHandleVerifier [0x0x7ff633a3fe1f+216527]
-	GetHandleVerifier [0x0x7ff633a27b24+117460]
-	GetHandleVerifier [0x0x7ff633a27cdf+117903]
-	GetHandleVerifier [0x0x7ff633a0dbb8+11112]
+	GetHandleVerifier [0x0x7ff6998fe8e5+80021]
+	GetHandleVerifier [0x0x7ff6998fe940+80112]
+	(No symbol) [0x0x7ff69968060f]
+	(No symbol) [0x0x7ff6996d8854]
+	(No symbol) [0x0x7ff6996d8b1c]
+	(No symbol) [0x0x7ff69972c927]
+	(No symbol) [0x0x7ff69970126f]
+	(No symbol) [0x0x7ff69972968a]
+	(No symbol) [0x0x7ff699701003]
+	(No symbol) [0x0x7ff6996c95d1]
+	(No symbol) [0x0x7ff6996ca3f3]
+	GetHandleVerifier [0x0x7ff699bbdc7d+2960429]
+	GetHandleVerifier [0x0x7ff699bb7f3a+2936554]
+	GetHandleVerifier [0x0x7ff699bd8977+3070247]
+	GetHandleVerifier [0x0x7ff6999183ce+185214]
+	GetHandleVerifier [0x0x7ff69991fe1f+216527]
+	GetHandleVerifier [0x0x7ff699907b24+117460]
+	GetHandleVerifier [0x0x7ff699907cdf+117903]
+	GetHandleVerifier [0x0x7ff6998edbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>£28.99</t>
+          <t>£28.43</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff633a1e8e5+80021]
-	GetHandleVerifier [0x0x7ff633a1e940+80112]
-	(No symbol) [0x0x7ff6337a060f]
-	(No symbol) [0x0x7ff6337f8854]
-	(No symbol) [0x0x7ff6337f8b1c]
-	(No symbol) [0x0x7ff63384c927]
-	(No symbol) [0x0x7ff63382126f]
-	(No symbol) [0x0x7ff63384968a]
-	(No symbol) [0x0x7ff633821003]
-	(No symbol) [0x0x7ff6337e95d1]
-	(No symbol) [0x0x7ff6337ea3f3]
-	GetHandleVerifier [0x0x7ff633cddc7d+2960429]
-	GetHandleVerifier [0x0x7ff633cd7f3a+2936554]
-	GetHandleVerifier [0x0x7ff633cf8977+3070247]
-	GetHandleVerifier [0x0x7ff633a383ce+185214]
-	GetHandleVerifier [0x0x7ff633a3fe1f+216527]
-	GetHandleVerifier [0x0x7ff633a27b24+117460]
-	GetHandleVerifier [0x0x7ff633a27cdf+117903]
-	GetHandleVerifier [0x0x7ff633a0dbb8+11112]
+	GetHandleVerifier [0x0x7ff6998fe8e5+80021]
+	GetHandleVerifier [0x0x7ff6998fe940+80112]
+	(No symbol) [0x0x7ff69968060f]
+	(No symbol) [0x0x7ff6996d8854]
+	(No symbol) [0x0x7ff6996d8b1c]
+	(No symbol) [0x0x7ff69972c927]
+	(No symbol) [0x0x7ff69970126f]
+	(No symbol) [0x0x7ff69972968a]
+	(No symbol) [0x0x7ff699701003]
+	(No symbol) [0x0x7ff6996c95d1]
+	(No symbol) [0x0x7ff6996ca3f3]
+	GetHandleVerifier [0x0x7ff699bbdc7d+2960429]
+	GetHandleVerifier [0x0x7ff699bb7f3a+2936554]
+	GetHandleVerifier [0x0x7ff699bd8977+3070247]
+	GetHandleVerifier [0x0x7ff6999183ce+185214]
+	GetHandleVerifier [0x0x7ff69991fe1f+216527]
+	GetHandleVerifier [0x0x7ff699907b24+117460]
+	GetHandleVerifier [0x0x7ff699907cdf+117903]
+	GetHandleVerifier [0x0x7ff6998edbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff633a1e8e5+80021]
-	GetHandleVerifier [0x0x7ff633a1e940+80112]
-	(No symbol) [0x0x7ff6337a060f]
-	(No symbol) [0x0x7ff6337f8854]
-	(No symbol) [0x0x7ff6337f8b1c]
-	(No symbol) [0x0x7ff63384c927]
-	(No symbol) [0x0x7ff63382126f]
-	(No symbol) [0x0x7ff63384968a]
-	(No symbol) [0x0x7ff633821003]
-	(No symbol) [0x0x7ff6337e95d1]
-	(No symbol) [0x0x7ff6337ea3f3]
-	GetHandleVerifier [0x0x7ff633cddc7d+2960429]
-	GetHandleVerifier [0x0x7ff633cd7f3a+2936554]
-	GetHandleVerifier [0x0x7ff633cf8977+3070247]
-	GetHandleVerifier [0x0x7ff633a383ce+185214]
-	GetHandleVerifier [0x0x7ff633a3fe1f+216527]
-	GetHandleVerifier [0x0x7ff633a27b24+117460]
-	GetHandleVerifier [0x0x7ff633a27cdf+117903]
-	GetHandleVerifier [0x0x7ff633a0dbb8+11112]
+	GetHandleVerifier [0x0x7ff6998fe8e5+80021]
+	GetHandleVerifier [0x0x7ff6998fe940+80112]
+	(No symbol) [0x0x7ff69968060f]
+	(No symbol) [0x0x7ff6996d8854]
+	(No symbol) [0x0x7ff6996d8b1c]
+	(No symbol) [0x0x7ff69972c927]
+	(No symbol) [0x0x7ff69970126f]
+	(No symbol) [0x0x7ff69972968a]
+	(No symbol) [0x0x7ff699701003]
+	(No symbol) [0x0x7ff6996c95d1]
+	(No symbol) [0x0x7ff6996ca3f3]
+	GetHandleVerifier [0x0x7ff699bbdc7d+2960429]
+	GetHandleVerifier [0x0x7ff699bb7f3a+2936554]
+	GetHandleVerifier [0x0x7ff699bd8977+3070247]
+	GetHandleVerifier [0x0x7ff6999183ce+185214]
+	GetHandleVerifier [0x0x7ff69991fe1f+216527]
+	GetHandleVerifier [0x0x7ff699907b24+117460]
+	GetHandleVerifier [0x0x7ff699907cdf+117903]
+	GetHandleVerifier [0x0x7ff6998edbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff633a1e8e5+80021]
-	GetHandleVerifier [0x0x7ff633a1e940+80112]
-	(No symbol) [0x0x7ff6337a060f]
-	(No symbol) [0x0x7ff6337f8854]
-	(No symbol) [0x0x7ff6337f8b1c]
-	(No symbol) [0x0x7ff63384c927]
-	(No symbol) [0x0x7ff63382126f]
-	(No symbol) [0x0x7ff63384968a]
-	(No symbol) [0x0x7ff633821003]
-	(No symbol) [0x0x7ff6337e95d1]
-	(No symbol) [0x0x7ff6337ea3f3]
-	GetHandleVerifier [0x0x7ff633cddc7d+2960429]
-	GetHandleVerifier [0x0x7ff633cd7f3a+2936554]
-	GetHandleVerifier [0x0x7ff633cf8977+3070247]
-	GetHandleVerifier [0x0x7ff633a383ce+185214]
-	GetHandleVerifier [0x0x7ff633a3fe1f+216527]
-	GetHandleVerifier [0x0x7ff633a27b24+117460]
-	GetHandleVerifier [0x0x7ff633a27cdf+117903]
-	GetHandleVerifier [0x0x7ff633a0dbb8+11112]
+	GetHandleVerifier [0x0x7ff7bc35e8e5+80021]
+	GetHandleVerifier [0x0x7ff7bc35e940+80112]
+	(No symbol) [0x0x7ff7bc0e060f]
+	(No symbol) [0x0x7ff7bc138854]
+	(No symbol) [0x0x7ff7bc138b1c]
+	(No symbol) [0x0x7ff7bc18c927]
+	(No symbol) [0x0x7ff7bc16126f]
+	(No symbol) [0x0x7ff7bc18968a]
+	(No symbol) [0x0x7ff7bc161003]
+	(No symbol) [0x0x7ff7bc1295d1]
+	(No symbol) [0x0x7ff7bc12a3f3]
+	GetHandleVerifier [0x0x7ff7bc61dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7bc617f3a+2936554]
+	GetHandleVerifier [0x0x7ff7bc638977+3070247]
+	GetHandleVerifier [0x0x7ff7bc3783ce+185214]
+	GetHandleVerifier [0x0x7ff7bc37fe1f+216527]
+	GetHandleVerifier [0x0x7ff7bc367b24+117460]
+	GetHandleVerifier [0x0x7ff7bc367cdf+117903]
+	GetHandleVerifier [0x0x7ff7bc34dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff633a1e8e5+80021]
-	GetHandleVerifier [0x0x7ff633a1e940+80112]
-	(No symbol) [0x0x7ff6337a060f]
-	(No symbol) [0x0x7ff6337f8854]
-	(No symbol) [0x0x7ff6337f8b1c]
-	(No symbol) [0x0x7ff63384c927]
-	(No symbol) [0x0x7ff63382126f]
-	(No symbol) [0x0x7ff63384968a]
-	(No symbol) [0x0x7ff633821003]
-	(No symbol) [0x0x7ff6337e95d1]
-	(No symbol) [0x0x7ff6337ea3f3]
-	GetHandleVerifier [0x0x7ff633cddc7d+2960429]
-	GetHandleVerifier [0x0x7ff633cd7f3a+2936554]
-	GetHandleVerifier [0x0x7ff633cf8977+3070247]
-	GetHandleVerifier [0x0x7ff633a383ce+185214]
-	GetHandleVerifier [0x0x7ff633a3fe1f+216527]
-	GetHandleVerifier [0x0x7ff633a27b24+117460]
-	GetHandleVerifier [0x0x7ff633a27cdf+117903]
-	GetHandleVerifier [0x0x7ff633a0dbb8+11112]
+	GetHandleVerifier [0x0x7ff7bc35e8e5+80021]
+	GetHandleVerifier [0x0x7ff7bc35e940+80112]
+	(No symbol) [0x0x7ff7bc0e060f]
+	(No symbol) [0x0x7ff7bc138854]
+	(No symbol) [0x0x7ff7bc138b1c]
+	(No symbol) [0x0x7ff7bc18c927]
+	(No symbol) [0x0x7ff7bc16126f]
+	(No symbol) [0x0x7ff7bc18968a]
+	(No symbol) [0x0x7ff7bc161003]
+	(No symbol) [0x0x7ff7bc1295d1]
+	(No symbol) [0x0x7ff7bc12a3f3]
+	GetHandleVerifier [0x0x7ff7bc61dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7bc617f3a+2936554]
+	GetHandleVerifier [0x0x7ff7bc638977+3070247]
+	GetHandleVerifier [0x0x7ff7bc3783ce+185214]
+	GetHandleVerifier [0x0x7ff7bc37fe1f+216527]
+	GetHandleVerifier [0x0x7ff7bc367b24+117460]
+	GetHandleVerifier [0x0x7ff7bc367cdf+117903]
+	GetHandleVerifier [0x0x7ff7bc34dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff633a1e8e5+80021]
-	GetHandleVerifier [0x0x7ff633a1e940+80112]
-	(No symbol) [0x0x7ff6337a060f]
-	(No symbol) [0x0x7ff6337f8854]
-	(No symbol) [0x0x7ff6337f8b1c]
-	(No symbol) [0x0x7ff63384c927]
-	(No symbol) [0x0x7ff63382126f]
-	(No symbol) [0x0x7ff63384968a]
-	(No symbol) [0x0x7ff633821003]
-	(No symbol) [0x0x7ff6337e95d1]
-	(No symbol) [0x0x7ff6337ea3f3]
-	GetHandleVerifier [0x0x7ff633cddc7d+2960429]
-	GetHandleVerifier [0x0x7ff633cd7f3a+2936554]
-	GetHandleVerifier [0x0x7ff633cf8977+3070247]
-	GetHandleVerifier [0x0x7ff633a383ce+185214]
-	GetHandleVerifier [0x0x7ff633a3fe1f+216527]
-	GetHandleVerifier [0x0x7ff633a27b24+117460]
-	GetHandleVerifier [0x0x7ff633a27cdf+117903]
-	GetHandleVerifier [0x0x7ff633a0dbb8+11112]
+	GetHandleVerifier [0x0x7ff7bc35e8e5+80021]
+	GetHandleVerifier [0x0x7ff7bc35e940+80112]
+	(No symbol) [0x0x7ff7bc0e060f]
+	(No symbol) [0x0x7ff7bc138854]
+	(No symbol) [0x0x7ff7bc138b1c]
+	(No symbol) [0x0x7ff7bc18c927]
+	(No symbol) [0x0x7ff7bc16126f]
+	(No symbol) [0x0x7ff7bc18968a]
+	(No symbol) [0x0x7ff7bc161003]
+	(No symbol) [0x0x7ff7bc1295d1]
+	(No symbol) [0x0x7ff7bc12a3f3]
+	GetHandleVerifier [0x0x7ff7bc61dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7bc617f3a+2936554]
+	GetHandleVerifier [0x0x7ff7bc638977+3070247]
+	GetHandleVerifier [0x0x7ff7bc3783ce+185214]
+	GetHandleVerifier [0x0x7ff7bc37fe1f+216527]
+	GetHandleVerifier [0x0x7ff7bc367b24+117460]
+	GetHandleVerifier [0x0x7ff7bc367cdf+117903]
+	GetHandleVerifier [0x0x7ff7bc34dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff633a1e8e5+80021]
-	GetHandleVerifier [0x0x7ff633a1e940+80112]
-	(No symbol) [0x0x7ff6337a060f]
-	(No symbol) [0x0x7ff6337f8854]
-	(No symbol) [0x0x7ff6337f8b1c]
-	(No symbol) [0x0x7ff63384c927]
-	(No symbol) [0x0x7ff63382126f]
-	(No symbol) [0x0x7ff63384968a]
-	(No symbol) [0x0x7ff633821003]
-	(No symbol) [0x0x7ff6337e95d1]
-	(No symbol) [0x0x7ff6337ea3f3]
-	GetHandleVerifier [0x0x7ff633cddc7d+2960429]
-	GetHandleVerifier [0x0x7ff633cd7f3a+2936554]
-	GetHandleVerifier [0x0x7ff633cf8977+3070247]
-	GetHandleVerifier [0x0x7ff633a383ce+185214]
-	GetHandleVerifier [0x0x7ff633a3fe1f+216527]
-	GetHandleVerifier [0x0x7ff633a27b24+117460]
-	GetHandleVerifier [0x0x7ff633a27cdf+117903]
-	GetHandleVerifier [0x0x7ff633a0dbb8+11112]
+	GetHandleVerifier [0x0x7ff7bc35e8e5+80021]
+	GetHandleVerifier [0x0x7ff7bc35e940+80112]
+	(No symbol) [0x0x7ff7bc0e060f]
+	(No symbol) [0x0x7ff7bc138854]
+	(No symbol) [0x0x7ff7bc138b1c]
+	(No symbol) [0x0x7ff7bc18c927]
+	(No symbol) [0x0x7ff7bc16126f]
+	(No symbol) [0x0x7ff7bc18968a]
+	(No symbol) [0x0x7ff7bc161003]
+	(No symbol) [0x0x7ff7bc1295d1]
+	(No symbol) [0x0x7ff7bc12a3f3]
+	GetHandleVerifier [0x0x7ff7bc61dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7bc617f3a+2936554]
+	GetHandleVerifier [0x0x7ff7bc638977+3070247]
+	GetHandleVerifier [0x0x7ff7bc3783ce+185214]
+	GetHandleVerifier [0x0x7ff7bc37fe1f+216527]
+	GetHandleVerifier [0x0x7ff7bc367b24+117460]
+	GetHandleVerifier [0x0x7ff7bc367cdf+117903]
+	GetHandleVerifier [0x0x7ff7bc34dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff633a1e8e5+80021]
-	GetHandleVerifier [0x0x7ff633a1e940+80112]
-	(No symbol) [0x0x7ff6337a060f]
-	(No symbol) [0x0x7ff6337f8854]
-	(No symbol) [0x0x7ff6337f8b1c]
-	(No symbol) [0x0x7ff63384c927]
-	(No symbol) [0x0x7ff63382126f]
-	(No symbol) [0x0x7ff63384968a]
-	(No symbol) [0x0x7ff633821003]
-	(No symbol) [0x0x7ff6337e95d1]
-	(No symbol) [0x0x7ff6337ea3f3]
-	GetHandleVerifier [0x0x7ff633cddc7d+2960429]
-	GetHandleVerifier [0x0x7ff633cd7f3a+2936554]
-	GetHandleVerifier [0x0x7ff633cf8977+3070247]
-	GetHandleVerifier [0x0x7ff633a383ce+185214]
-	GetHandleVerifier [0x0x7ff633a3fe1f+216527]
-	GetHandleVerifier [0x0x7ff633a27b24+117460]
-	GetHandleVerifier [0x0x7ff633a27cdf+117903]
-	GetHandleVerifier [0x0x7ff633a0dbb8+11112]
+	GetHandleVerifier [0x0x7ff7bc35e8e5+80021]
+	GetHandleVerifier [0x0x7ff7bc35e940+80112]
+	(No symbol) [0x0x7ff7bc0e060f]
+	(No symbol) [0x0x7ff7bc138854]
+	(No symbol) [0x0x7ff7bc138b1c]
+	(No symbol) [0x0x7ff7bc18c927]
+	(No symbol) [0x0x7ff7bc16126f]
+	(No symbol) [0x0x7ff7bc18968a]
+	(No symbol) [0x0x7ff7bc161003]
+	(No symbol) [0x0x7ff7bc1295d1]
+	(No symbol) [0x0x7ff7bc12a3f3]
+	GetHandleVerifier [0x0x7ff7bc61dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7bc617f3a+2936554]
+	GetHandleVerifier [0x0x7ff7bc638977+3070247]
+	GetHandleVerifier [0x0x7ff7bc3783ce+185214]
+	GetHandleVerifier [0x0x7ff7bc37fe1f+216527]
+	GetHandleVerifier [0x0x7ff7bc367b24+117460]
+	GetHandleVerifier [0x0x7ff7bc367cdf+117903]
+	GetHandleVerifier [0x0x7ff7bc34dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff633a1e8e5+80021]
-	GetHandleVerifier [0x0x7ff633a1e940+80112]
-	(No symbol) [0x0x7ff6337a060f]
-	(No symbol) [0x0x7ff6337f8854]
-	(No symbol) [0x0x7ff6337f8b1c]
-	(No symbol) [0x0x7ff63384c927]
-	(No symbol) [0x0x7ff63382126f]
-	(No symbol) [0x0x7ff63384968a]
-	(No symbol) [0x0x7ff633821003]
-	(No symbol) [0x0x7ff6337e95d1]
-	(No symbol) [0x0x7ff6337ea3f3]
-	GetHandleVerifier [0x0x7ff633cddc7d+2960429]
-	GetHandleVerifier [0x0x7ff633cd7f3a+2936554]
-	GetHandleVerifier [0x0x7ff633cf8977+3070247]
-	GetHandleVerifier [0x0x7ff633a383ce+185214]
-	GetHandleVerifier [0x0x7ff633a3fe1f+216527]
-	GetHandleVerifier [0x0x7ff633a27b24+117460]
-	GetHandleVerifier [0x0x7ff633a27cdf+117903]
-	GetHandleVerifier [0x0x7ff633a0dbb8+11112]
+	GetHandleVerifier [0x0x7ff7bc35e8e5+80021]
+	GetHandleVerifier [0x0x7ff7bc35e940+80112]
+	(No symbol) [0x0x7ff7bc0e060f]
+	(No symbol) [0x0x7ff7bc138854]
+	(No symbol) [0x0x7ff7bc138b1c]
+	(No symbol) [0x0x7ff7bc18c927]
+	(No symbol) [0x0x7ff7bc16126f]
+	(No symbol) [0x0x7ff7bc18968a]
+	(No symbol) [0x0x7ff7bc161003]
+	(No symbol) [0x0x7ff7bc1295d1]
+	(No symbol) [0x0x7ff7bc12a3f3]
+	GetHandleVerifier [0x0x7ff7bc61dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7bc617f3a+2936554]
+	GetHandleVerifier [0x0x7ff7bc638977+3070247]
+	GetHandleVerifier [0x0x7ff7bc3783ce+185214]
+	GetHandleVerifier [0x0x7ff7bc37fe1f+216527]
+	GetHandleVerifier [0x0x7ff7bc367b24+117460]
+	GetHandleVerifier [0x0x7ff7bc367cdf+117903]
+	GetHandleVerifier [0x0x7ff7bc34dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>£1162.4</t>
+          <t>£1133.6</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
